--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -53,24 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
   </si>
   <si>
     <t>В0233РС</t>
@@ -161,8 +143,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -248,11 +231,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -260,9 +244,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,20 +600,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46146</v>
       </c>
       <c r="B2">
         <v>1147</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>35.789</v>
@@ -647,7 +631,7 @@
         <v>54.4</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -657,20 +641,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="2">
+        <v>46147</v>
       </c>
       <c r="B3">
         <v>1147</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>83</v>
@@ -688,7 +672,7 @@
         <v>149.4</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -698,20 +682,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
+      <c r="A4" s="2">
+        <v>46149</v>
       </c>
       <c r="B4">
         <v>1147</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>29.819</v>
@@ -729,7 +713,7 @@
         <v>24.75</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -739,20 +723,20 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>16</v>
+      <c r="A5" s="2">
+        <v>46150</v>
       </c>
       <c r="B5">
         <v>1146</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>29</v>
@@ -770,7 +754,7 @@
         <v>44.37</v>
       </c>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -780,20 +764,20 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>17</v>
+      <c r="A6" s="2">
+        <v>46154</v>
       </c>
       <c r="B6">
         <v>1147</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>27.622</v>
@@ -811,7 +795,7 @@
         <v>22.65</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -821,20 +805,20 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>18</v>
+      <c r="A7" s="2">
+        <v>46156</v>
       </c>
       <c r="B7">
         <v>1147</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>33.432</v>
@@ -852,7 +836,7 @@
         <v>27.08</v>
       </c>
       <c r="K7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -862,126 +846,126 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="3" t="s">
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="6">
+        <v>90.873</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.8096</v>
+      </c>
+      <c r="E12" s="6">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="F12" s="6">
+        <v>74.48</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="6">
+        <v>83</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1.77</v>
+      </c>
+      <c r="E13" s="6">
+        <v>146.91</v>
+      </c>
+      <c r="F13" s="6">
+        <v>149.4</v>
+      </c>
+      <c r="G13" s="6">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="6">
+        <v>64.789</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1.4945</v>
+      </c>
+      <c r="E14" s="6">
+        <v>96.83</v>
+      </c>
+      <c r="F14" s="6">
+        <v>98.77</v>
+      </c>
+      <c r="G14" s="6">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="5">
-        <v>90.873</v>
-      </c>
-      <c r="C12" s="5">
-        <v>3</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0.8096</v>
-      </c>
-      <c r="E12" s="5">
-        <v>73.56999999999999</v>
-      </c>
-      <c r="F12" s="5">
-        <v>74.48</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="5">
-        <v>83</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1.77</v>
-      </c>
-      <c r="E13" s="5">
-        <v>146.91</v>
-      </c>
-      <c r="F13" s="5">
-        <v>149.4</v>
-      </c>
-      <c r="G13" s="5">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="5">
-        <v>64.789</v>
-      </c>
-      <c r="C14" s="5">
-        <v>2</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1.4945</v>
-      </c>
-      <c r="E14" s="5">
-        <v>96.83</v>
-      </c>
-      <c r="F14" s="5">
-        <v>98.77</v>
-      </c>
-      <c r="G14" s="5">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <v>238.662</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>6</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8">
         <v>317.31</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="8">
         <v>322.65</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="8">
         <v>5.34</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -167,7 +167,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,12 +177,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,17 +227,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,70 +46,46 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>В8894ХВ</t>
+  </si>
+  <si>
+    <t>В0235РС</t>
   </si>
   <si>
     <t>В7240ВР</t>
   </si>
   <si>
-    <t>В0235РС</t>
-  </si>
-  <si>
-    <t>В0233РС</t>
+    <t>В8992ВР</t>
+  </si>
+  <si>
+    <t>78970155027720576</t>
+  </si>
+  <si>
+    <t>78970155027720543</t>
   </si>
   <si>
     <t>78970155027720568</t>
   </si>
   <si>
-    <t>78970155027720543</t>
-  </si>
-  <si>
-    <t>78970155027720535</t>
+    <t>78970155027720550</t>
+  </si>
+  <si>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>13:44:00</t>
-  </si>
-  <si>
-    <t>09:25:00</t>
-  </si>
-  <si>
-    <t>15:13:00</t>
-  </si>
-  <si>
-    <t>09:59:00</t>
-  </si>
-  <si>
-    <t>3232151448 3232151448</t>
-  </si>
-  <si>
-    <t>3232409182 3232409182</t>
-  </si>
-  <si>
-    <t>3232525858 3232525858</t>
-  </si>
-  <si>
-    <t>3232567742 3232567742</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА</t>
@@ -532,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -541,17 +514,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -585,283 +555,398 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46162</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H2">
+        <v>138.73</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J2">
+        <v>141.23</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>22</v>
-      </c>
-      <c r="F2">
-        <v>27.27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>0.78</v>
-      </c>
-      <c r="I2" s="1">
-        <v>21.27</v>
-      </c>
-      <c r="J2">
-        <v>0.79</v>
-      </c>
-      <c r="K2" s="1">
-        <v>21.54</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
-        <v>24</v>
+      <c r="G3" s="1">
+        <v>1.54</v>
       </c>
       <c r="H3">
-        <v>1.54</v>
+        <v>30.8</v>
       </c>
       <c r="I3" s="1">
-        <v>30.8</v>
+        <v>1.57</v>
       </c>
       <c r="J3">
-        <v>1.57</v>
-      </c>
-      <c r="K3" s="1">
         <v>31.4</v>
       </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
+      <c r="K3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="3">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>29.6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
+        <v>30.77</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.73</v>
       </c>
       <c r="H4">
-        <v>0.76</v>
+        <v>22.46</v>
       </c>
       <c r="I4" s="1">
-        <v>22.5</v>
+        <v>0.74</v>
       </c>
       <c r="J4">
-        <v>0.77</v>
-      </c>
-      <c r="K4" s="1">
-        <v>22.79</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
+        <v>22.77</v>
+      </c>
+      <c r="K4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="3">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
       </c>
       <c r="F5">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
+        <v>27.08</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="H5">
+        <v>19.77</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J5">
+        <v>20.04</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>25.83</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H6">
+        <v>18.34</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J6">
+        <v>18.6</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>28.58</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H7">
+        <v>19.43</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J7">
+        <v>19.72</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H8">
+        <v>15.3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J8">
+        <v>15.6</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H9">
+        <v>30.6</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J9">
+        <v>31.2</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H5">
-        <v>1.54</v>
-      </c>
-      <c r="I5" s="1">
-        <v>53.9</v>
-      </c>
-      <c r="J5">
-        <v>1.57</v>
-      </c>
-      <c r="K5" s="1">
-        <v>54.95</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="E13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="7">
+        <v>112.26</v>
+      </c>
+      <c r="C14" s="7">
+        <v>4</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.7126</v>
+      </c>
+      <c r="E14" s="7">
+        <v>80</v>
+      </c>
+      <c r="F14" s="7">
+        <v>81.13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="7">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1.66</v>
+      </c>
+      <c r="E15" s="7">
+        <v>138.73</v>
+      </c>
+      <c r="F15" s="7">
+        <v>141.23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="7">
+        <v>50</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1.534</v>
+      </c>
+      <c r="E16" s="7">
+        <v>76.7</v>
+      </c>
+      <c r="F16" s="7">
+        <v>78.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="10">
+        <v>245.83</v>
+      </c>
+      <c r="C17" s="10">
         <v>8</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="7">
-        <v>56.87</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.7697000000000001</v>
-      </c>
-      <c r="E10" s="7">
-        <v>43.77</v>
-      </c>
-      <c r="F10" s="7">
-        <v>44.33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="7">
-        <v>55</v>
-      </c>
-      <c r="C11" s="7">
-        <v>2</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.54</v>
-      </c>
-      <c r="E11" s="7">
-        <v>84.7</v>
-      </c>
-      <c r="F11" s="7">
-        <v>86.34999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="10">
-        <v>111.87</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>128.47</v>
-      </c>
-      <c r="F12" s="10">
-        <v>130.68</v>
+      <c r="D17" s="8"/>
+      <c r="E17" s="10">
+        <v>295.43</v>
+      </c>
+      <c r="F17" s="10">
+        <v>300.56</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="40">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
@@ -86,6 +92,30 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>08:36</t>
+  </si>
+  <si>
+    <t>10:36</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>11:13</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>12:38</t>
+  </si>
+  <si>
+    <t>12:44</t>
+  </si>
+  <si>
+    <t>13:50</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА</t>
@@ -505,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,10 +548,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,22 +587,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>83.56999999999999</v>
@@ -587,25 +625,31 @@
       <c r="J2">
         <v>141.23</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>111523</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46174</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>20</v>
@@ -622,25 +666,31 @@
       <c r="J3">
         <v>31.4</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>190688</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46176</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>30.77</v>
@@ -657,25 +707,31 @@
       <c r="J4">
         <v>22.77</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>192262</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46178</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>27.08</v>
@@ -692,25 +748,31 @@
       <c r="J5">
         <v>20.04</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>138822</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46181</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>25.83</v>
@@ -727,25 +789,31 @@
       <c r="J6">
         <v>18.6</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>195072</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46184</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>28.58</v>
@@ -762,25 +830,31 @@
       <c r="J7">
         <v>19.72</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>113899</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46184</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -797,25 +871,31 @@
       <c r="J8">
         <v>15.6</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M8">
+        <v>113900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46185</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F9">
         <v>20</v>
@@ -832,13 +912,19 @@
       <c r="J9">
         <v>31.2</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="M9">
+        <v>141392</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -846,18 +932,18 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>7</v>
@@ -866,9 +952,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="7">
         <v>112.26</v>
@@ -886,9 +972,9 @@
         <v>81.13</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:13">
       <c r="A15" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B15" s="7">
         <v>83.56999999999999</v>
@@ -906,9 +992,9 @@
         <v>141.23</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:13">
       <c r="A16" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7">
         <v>50</v>
@@ -928,7 +1014,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="9" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B17" s="10">
         <v>245.83</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -49,73 +49,49 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
     <t>Варна Сливница</t>
   </si>
   <si>
-    <t>В8894ХВ</t>
+    <t>В7240ВР</t>
   </si>
   <si>
     <t>В0235РС</t>
   </si>
   <si>
-    <t>В7240ВР</t>
-  </si>
-  <si>
-    <t>В8992ВР</t>
-  </si>
-  <si>
-    <t>78970155027720576</t>
+    <t>В0233РС</t>
+  </si>
+  <si>
+    <t>78970155027720568</t>
   </si>
   <si>
     <t>78970155027720543</t>
   </si>
   <si>
-    <t>78970155027720568</t>
-  </si>
-  <si>
-    <t>78970155027720550</t>
-  </si>
-  <si>
-    <t>DIESEL EKONOMY</t>
+    <t>78970155027720535</t>
+  </si>
+  <si>
+    <t>E GAS LPG</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>08:36</t>
-  </si>
-  <si>
-    <t>10:36</t>
-  </si>
-  <si>
-    <t>12:29</t>
-  </si>
-  <si>
-    <t>11:13</t>
-  </si>
-  <si>
-    <t>09:08</t>
-  </si>
-  <si>
-    <t>12:38</t>
-  </si>
-  <si>
-    <t>12:44</t>
-  </si>
-  <si>
-    <t>13:50</t>
+    <t>2026-06-18 08:24:49</t>
+  </si>
+  <si>
+    <t>2026-06-23 09:06:36</t>
+  </si>
+  <si>
+    <t>2026-06-24 08:33:17</t>
+  </si>
+  <si>
+    <t>2026-06-24 12:12:21</t>
+  </si>
+  <si>
+    <t>2026-06-25 14:29:36</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА</t>
@@ -535,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -548,12 +524,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -587,452 +561,273 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46191</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>30.8</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>20.02</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>20.33</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46196</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>83.56999999999999</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="H2">
-        <v>138.73</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J2">
-        <v>141.23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>111523</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
       <c r="G3" s="1">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="H3">
-        <v>30.8</v>
+        <v>29.6</v>
       </c>
       <c r="I3" s="1">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="J3">
-        <v>31.4</v>
+        <v>30.2</v>
       </c>
       <c r="K3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>37.58</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H4">
+        <v>24.43</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J4">
+        <v>24.8</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H5">
+        <v>51.8</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J5">
+        <v>52.85</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46198</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H6">
+        <v>29.6</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J6">
+        <v>30.2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>190688</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46176</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4">
-        <v>30.77</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="H4">
-        <v>22.46</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="J4">
-        <v>22.77</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="B10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>192262</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46178</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5">
-        <v>27.08</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="H5">
-        <v>19.77</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="J5">
-        <v>20.04</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="C10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>138822</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46181</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6">
-        <v>25.83</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="H6">
-        <v>18.34</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="J6">
-        <v>18.6</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="D10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>195072</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>28.58</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="H7">
-        <v>19.43</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J7">
-        <v>19.72</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="E10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="7">
+        <v>75</v>
+      </c>
+      <c r="C11" s="7">
+        <v>3</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.48</v>
+      </c>
+      <c r="E11" s="7">
+        <v>111</v>
+      </c>
+      <c r="F11" s="7">
+        <v>113.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7">
+        <v>68.38</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="E12" s="7">
+        <v>44.45</v>
+      </c>
+      <c r="F12" s="7">
+        <v>45.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>113899</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8">
-        <v>10</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H8">
-        <v>15.3</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J8">
-        <v>15.6</v>
-      </c>
-      <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>113900</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3">
-        <v>46185</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H9">
-        <v>30.6</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J9">
-        <v>31.2</v>
-      </c>
-      <c r="K9" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>141392</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="7">
-        <v>112.26</v>
-      </c>
-      <c r="C14" s="7">
-        <v>4</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0.7126</v>
-      </c>
-      <c r="E14" s="7">
-        <v>80</v>
-      </c>
-      <c r="F14" s="7">
-        <v>81.13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="7">
-        <v>83.56999999999999</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1.66</v>
-      </c>
-      <c r="E15" s="7">
-        <v>138.73</v>
-      </c>
-      <c r="F15" s="7">
-        <v>141.23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="7">
-        <v>50</v>
-      </c>
-      <c r="C16" s="7">
-        <v>3</v>
-      </c>
-      <c r="D16" s="8">
-        <v>1.534</v>
-      </c>
-      <c r="E16" s="7">
-        <v>76.7</v>
-      </c>
-      <c r="F16" s="7">
-        <v>78.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="10">
-        <v>245.83</v>
-      </c>
-      <c r="C17" s="10">
-        <v>8</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="10">
-        <v>295.43</v>
-      </c>
-      <c r="F17" s="10">
-        <v>300.56</v>
+      <c r="B13" s="10">
+        <v>143.38</v>
+      </c>
+      <c r="C13" s="10">
+        <v>5</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>155.45</v>
+      </c>
+      <c r="F13" s="10">
+        <v>158.38</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,10 +52,16 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>В7240ВР</t>
@@ -79,19 +88,49 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-18 08:24:49</t>
-  </si>
-  <si>
-    <t>2026-06-23 09:06:36</t>
-  </si>
-  <si>
-    <t>2026-06-24 08:33:17</t>
-  </si>
-  <si>
-    <t>2026-06-24 12:12:21</t>
-  </si>
-  <si>
-    <t>2026-06-25 14:29:36</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:25:00</t>
+  </si>
+  <si>
+    <t>09:07:00</t>
+  </si>
+  <si>
+    <t>08:33:00</t>
+  </si>
+  <si>
+    <t>12:12:00</t>
+  </si>
+  <si>
+    <t>14:29:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>3233502650 3233502650</t>
+  </si>
+  <si>
+    <t>3233748023 3233748023</t>
+  </si>
+  <si>
+    <t>3233800671 3233800671</t>
+  </si>
+  <si>
+    <t>3233805379 3233805379</t>
+  </si>
+  <si>
+    <t>3233836528 3233836528</t>
+  </si>
+  <si>
+    <t>3234096957 3234096957</t>
+  </si>
+  <si>
+    <t>3234099136 3234099136</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА</t>
@@ -511,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,14 +559,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -561,273 +603,415 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46191</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>30.8</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
         <v>0.65</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>20.02</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>20.33</v>
       </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46196</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3">
         <v>1.48</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>29.6</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.51</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>30.2</v>
       </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46197</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>37.58</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>24.43</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>0.66</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>24.8</v>
       </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46197</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>35</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5">
         <v>1.48</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>51.8</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.51</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>52.85</v>
       </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46198</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>20</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6">
         <v>1.48</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>29.6</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.51</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>30.2</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>1.47</v>
+      </c>
+      <c r="I7" s="1">
+        <v>36.75</v>
+      </c>
+      <c r="J7">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="L7" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8">
+        <v>37.04</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>0.65</v>
+      </c>
+      <c r="I8" s="1">
+        <v>24.08</v>
+      </c>
+      <c r="J8">
+        <v>0.66</v>
+      </c>
+      <c r="K8" s="1">
+        <v>24.45</v>
+      </c>
+      <c r="L8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="7">
+        <v>105.42</v>
+      </c>
+      <c r="C13" s="7">
+        <v>3</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.6501</v>
+      </c>
+      <c r="E13" s="7">
+        <v>68.53</v>
+      </c>
+      <c r="F13" s="7">
+        <v>69.58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="7">
+        <v>100</v>
+      </c>
+      <c r="C14" s="7">
+        <v>4</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1.4775</v>
+      </c>
+      <c r="E14" s="7">
+        <v>147.75</v>
+      </c>
+      <c r="F14" s="7">
+        <v>150.75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="10">
+        <v>205.42</v>
+      </c>
+      <c r="C15" s="10">
         <v>7</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="7">
-        <v>75</v>
-      </c>
-      <c r="C11" s="7">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.48</v>
-      </c>
-      <c r="E11" s="7">
-        <v>111</v>
-      </c>
-      <c r="F11" s="7">
-        <v>113.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="7">
-        <v>68.38</v>
-      </c>
-      <c r="C12" s="7">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="E12" s="7">
-        <v>44.45</v>
-      </c>
-      <c r="F12" s="7">
-        <v>45.13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="10">
-        <v>143.38</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>155.45</v>
-      </c>
-      <c r="F13" s="10">
-        <v>158.38</v>
+      <c r="D15" s="8"/>
+      <c r="E15" s="10">
+        <v>216.28</v>
+      </c>
+      <c r="F15" s="10">
+        <v>220.33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="36">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,10 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>В7240ВР</t>
@@ -88,49 +85,25 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>08:25:00</t>
-  </si>
-  <si>
-    <t>09:07:00</t>
-  </si>
-  <si>
-    <t>08:33:00</t>
-  </si>
-  <si>
-    <t>12:12:00</t>
-  </si>
-  <si>
-    <t>14:29:00</t>
-  </si>
-  <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
-    <t>14:15:00</t>
-  </si>
-  <si>
-    <t>3233502650 3233502650</t>
-  </si>
-  <si>
-    <t>3233748023 3233748023</t>
-  </si>
-  <si>
-    <t>3233800671 3233800671</t>
-  </si>
-  <si>
-    <t>3233805379 3233805379</t>
-  </si>
-  <si>
-    <t>3233836528 3233836528</t>
-  </si>
-  <si>
-    <t>3234096957 3234096957</t>
-  </si>
-  <si>
-    <t>3234099136 3234099136</t>
+    <t>08:24</t>
+  </si>
+  <si>
+    <t>09:06</t>
+  </si>
+  <si>
+    <t>08:33</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>14:29</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>14:15</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА</t>
@@ -550,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -559,17 +532,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -609,321 +581,297 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46191</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>30.8</v>
       </c>
-      <c r="G2" t="s">
-        <v>24</v>
+      <c r="G2" s="1">
+        <v>0.65</v>
       </c>
       <c r="H2">
-        <v>0.65</v>
+        <v>20.02</v>
       </c>
       <c r="I2" s="1">
-        <v>20.02</v>
+        <v>0.66</v>
       </c>
       <c r="J2">
-        <v>0.66</v>
-      </c>
-      <c r="K2" s="1">
         <v>20.33</v>
       </c>
-      <c r="L2" t="s">
-        <v>25</v>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>116152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46196</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H3">
+        <v>29.6</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J3">
+        <v>30.2</v>
+      </c>
+      <c r="K3" t="s">
         <v>24</v>
       </c>
-      <c r="H3">
-        <v>1.48</v>
-      </c>
-      <c r="I3" s="1">
-        <v>29.6</v>
-      </c>
-      <c r="J3">
-        <v>1.51</v>
-      </c>
-      <c r="K3" s="1">
-        <v>30.2</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>49130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46197</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>37.58</v>
       </c>
-      <c r="G4" t="s">
-        <v>24</v>
+      <c r="G4" s="1">
+        <v>0.65</v>
       </c>
       <c r="H4">
-        <v>0.65</v>
+        <v>24.43</v>
       </c>
       <c r="I4" s="1">
-        <v>24.43</v>
+        <v>0.66</v>
       </c>
       <c r="J4">
-        <v>0.66</v>
-      </c>
-      <c r="K4" s="1">
         <v>24.8</v>
       </c>
-      <c r="L4" t="s">
-        <v>27</v>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>118423</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46197</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>35</v>
       </c>
-      <c r="G5" t="s">
-        <v>24</v>
+      <c r="G5" s="1">
+        <v>1.48</v>
       </c>
       <c r="H5">
-        <v>1.48</v>
+        <v>51.8</v>
       </c>
       <c r="I5" s="1">
-        <v>51.8</v>
+        <v>1.51</v>
       </c>
       <c r="J5">
-        <v>1.51</v>
-      </c>
-      <c r="K5" s="1">
         <v>52.85</v>
       </c>
-      <c r="L5" t="s">
-        <v>28</v>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>204479</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46198</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
-        <v>24</v>
+      <c r="G6" s="1">
+        <v>1.48</v>
       </c>
       <c r="H6">
-        <v>1.48</v>
+        <v>29.6</v>
       </c>
       <c r="I6" s="1">
-        <v>29.6</v>
+        <v>1.51</v>
       </c>
       <c r="J6">
-        <v>1.51</v>
-      </c>
-      <c r="K6" s="1">
         <v>30.2</v>
       </c>
-      <c r="L6" t="s">
-        <v>29</v>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>145651</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46203</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>25</v>
       </c>
-      <c r="G7" t="s">
-        <v>24</v>
+      <c r="G7" s="1">
+        <v>1.47</v>
       </c>
       <c r="H7">
-        <v>1.47</v>
+        <v>36.75</v>
       </c>
       <c r="I7" s="1">
-        <v>36.75</v>
+        <v>1.5</v>
       </c>
       <c r="J7">
-        <v>1.5</v>
-      </c>
-      <c r="K7" s="1">
         <v>37.5</v>
       </c>
-      <c r="L7" t="s">
-        <v>30</v>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>208213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46203</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8">
         <v>37.04</v>
       </c>
-      <c r="G8" t="s">
-        <v>24</v>
+      <c r="G8" s="1">
+        <v>0.65</v>
       </c>
       <c r="H8">
-        <v>0.65</v>
+        <v>24.08</v>
       </c>
       <c r="I8" s="1">
-        <v>24.08</v>
+        <v>0.66</v>
       </c>
       <c r="J8">
-        <v>0.66</v>
-      </c>
-      <c r="K8" s="1">
         <v>24.45</v>
       </c>
-      <c r="L8" t="s">
-        <v>31</v>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>208280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -931,29 +879,29 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:13">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="7">
         <v>105.42</v>
@@ -971,9 +919,9 @@
         <v>69.58</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7">
         <v>100</v>
@@ -991,9 +939,9 @@
         <v>150.75</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:13">
       <c r="A15" s="9" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B15" s="10">
         <v>205.42</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="49">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,61 +55,94 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>В7240ВР</t>
+  </si>
+  <si>
+    <t>В8992ВР</t>
   </si>
   <si>
     <t>В0235РС</t>
   </si>
   <si>
-    <t>В8894ХВ</t>
-  </si>
-  <si>
-    <t>В7240ВР</t>
-  </si>
-  <si>
-    <t>В8992ВР</t>
+    <t>В0233РС</t>
+  </si>
+  <si>
+    <t>78970155027720568</t>
+  </si>
+  <si>
+    <t>78970155027720550</t>
   </si>
   <si>
     <t>78970155027720543</t>
   </si>
   <si>
-    <t>78970155027720576</t>
-  </si>
-  <si>
-    <t>78970155027720568</t>
-  </si>
-  <si>
-    <t>78970155027720550</t>
+    <t>78970155027720535</t>
+  </si>
+  <si>
+    <t>E GAS LPG</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>2026-07-03 10:11:41</t>
-  </si>
-  <si>
-    <t>2026-07-07 08:30:03</t>
-  </si>
-  <si>
-    <t>2026-07-07 09:41:49</t>
-  </si>
-  <si>
-    <t>2026-07-08 11:25:05</t>
-  </si>
-  <si>
-    <t>2026-07-08 11:25:06</t>
-  </si>
-  <si>
-    <t>2026-07-10 10:12:21</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:03:00</t>
+  </si>
+  <si>
+    <t>12:54:00</t>
+  </si>
+  <si>
+    <t>14:04:00</t>
+  </si>
+  <si>
+    <t>11:22:00</t>
+  </si>
+  <si>
+    <t>11:25:00</t>
+  </si>
+  <si>
+    <t>14:28:00</t>
+  </si>
+  <si>
+    <t>11:45:00</t>
+  </si>
+  <si>
+    <t>14:36:00</t>
+  </si>
+  <si>
+    <t>3234862370 3234862370</t>
+  </si>
+  <si>
+    <t>3235107979 3235107979</t>
+  </si>
+  <si>
+    <t>3235140740 3235140740</t>
+  </si>
+  <si>
+    <t>3235182898 3235182898</t>
+  </si>
+  <si>
+    <t>3235182899 3235182899</t>
+  </si>
+  <si>
+    <t>3235415080 3235415080</t>
+  </si>
+  <si>
+    <t>3235556136 3235556136</t>
+  </si>
+  <si>
+    <t>3235622040 3235622040</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА</t>
@@ -526,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -535,15 +571,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -580,346 +618,456 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46206</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2">
+        <v>29.48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>18.28</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>18.57</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H2">
-        <v>29.4</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J2">
-        <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2">
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>27.7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3">
+        <v>0.63</v>
+      </c>
+      <c r="I3" s="1">
+        <v>17.45</v>
+      </c>
+      <c r="J3">
+        <v>0.64</v>
+      </c>
+      <c r="K3" s="1">
+        <v>17.73</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46210</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3">
-        <v>83</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="H3">
-        <v>123.67</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J3">
-        <v>126.16</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46210</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4">
-        <v>28.22</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.62</v>
+        <v>27.16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
       </c>
       <c r="H4">
-        <v>17.5</v>
+        <v>0.63</v>
       </c>
       <c r="I4" s="1">
+        <v>17.11</v>
+      </c>
+      <c r="J4">
+        <v>0.64</v>
+      </c>
+      <c r="K4" s="1">
+        <v>17.38</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>1.51</v>
+      </c>
+      <c r="I5" s="1">
+        <v>30.2</v>
+      </c>
+      <c r="J5">
+        <v>1.54</v>
+      </c>
+      <c r="K5" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6">
+        <v>1.51</v>
+      </c>
+      <c r="I6" s="1">
+        <v>58.89</v>
+      </c>
+      <c r="J6">
+        <v>1.54</v>
+      </c>
+      <c r="K6" s="1">
+        <v>60.06</v>
+      </c>
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46230</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7">
+        <v>1.53</v>
+      </c>
+      <c r="I7" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="J7">
+        <v>1.56</v>
+      </c>
+      <c r="K7" s="1">
+        <v>31.2</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>1.52</v>
+      </c>
+      <c r="I8" s="1">
+        <v>30.4</v>
+      </c>
+      <c r="J8">
+        <v>1.55</v>
+      </c>
+      <c r="K8" s="1">
+        <v>31</v>
+      </c>
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9">
+        <v>36.33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9">
         <v>0.63</v>
       </c>
-      <c r="J4">
-        <v>17.78</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4">
+      <c r="I9" s="1">
+        <v>22.89</v>
+      </c>
+      <c r="J9">
+        <v>0.64</v>
+      </c>
+      <c r="K9" s="1">
+        <v>23.25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>46211</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
+      <c r="N9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="H5">
-        <v>14.6</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J5">
-        <v>14.9</v>
-      </c>
-      <c r="K5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3">
-        <v>46211</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F6">
-        <v>30.97</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H6">
-        <v>19.2</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J6">
-        <v>19.51</v>
-      </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3">
-        <v>46213</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>32.17</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H7">
-        <v>19.95</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J7">
-        <v>20.27</v>
-      </c>
-      <c r="K7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="7">
-        <v>91.36</v>
-      </c>
-      <c r="C12" s="7">
-        <v>3</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.6201</v>
-      </c>
-      <c r="E12" s="7">
-        <v>56.65</v>
-      </c>
-      <c r="F12" s="7">
-        <v>57.56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="7">
-        <v>83</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1.49</v>
-      </c>
-      <c r="E13" s="7">
-        <v>123.67</v>
-      </c>
-      <c r="F13" s="7">
-        <v>126.16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="B14" s="7">
-        <v>30</v>
+        <v>120.67</v>
       </c>
       <c r="C14" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="8">
-        <v>1.4667</v>
+        <v>0.6276</v>
       </c>
       <c r="E14" s="7">
-        <v>44</v>
+        <v>75.73</v>
       </c>
       <c r="F14" s="7">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="10">
-        <v>204.36</v>
-      </c>
-      <c r="C15" s="10">
-        <v>6</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="10">
-        <v>224.32</v>
-      </c>
-      <c r="F15" s="10">
-        <v>228.62</v>
+        <v>76.93000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="7">
+        <v>99</v>
+      </c>
+      <c r="C15" s="7">
+        <v>4</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1.5161</v>
+      </c>
+      <c r="E15" s="7">
+        <v>150.09</v>
+      </c>
+      <c r="F15" s="7">
+        <v>153.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="10">
+        <v>219.67</v>
+      </c>
+      <c r="C16" s="10">
+        <v>8</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="10">
+        <v>225.82</v>
+      </c>
+      <c r="F16" s="10">
+        <v>229.99</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -170,7 +170,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1018,7 +1018,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="8">
-        <v>0.6276</v>
+        <v>0.627579</v>
       </c>
       <c r="E14" s="7">
         <v>75.73</v>
@@ -1038,7 +1038,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="8">
-        <v>1.5161</v>
+        <v>1.516061</v>
       </c>
       <c r="E15" s="7">
         <v>150.09</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -562,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -575,13 +578,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -624,362 +627,389 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>29.48</v>
+        <v>29.476</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.62</v>
       </c>
-      <c r="I2" s="1">
-        <v>18.28</v>
-      </c>
       <c r="J2">
+        <v>18.27512</v>
+      </c>
+      <c r="K2" s="1">
         <v>0.63</v>
       </c>
-      <c r="K2" s="1">
-        <v>18.57</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>18.56988</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46224</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>27.7</v>
+        <v>27.703</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.63</v>
       </c>
-      <c r="I3" s="1">
-        <v>17.45</v>
-      </c>
       <c r="J3">
+        <v>17.45289</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.64</v>
       </c>
-      <c r="K3" s="1">
-        <v>17.73</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>17.72992</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46224</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>27.16</v>
+        <v>27.156</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
         <v>0.63</v>
       </c>
-      <c r="I4" s="1">
-        <v>17.11</v>
-      </c>
       <c r="J4">
+        <v>17.10828</v>
+      </c>
+      <c r="K4" s="1">
         <v>0.64</v>
       </c>
-      <c r="K4" s="1">
-        <v>17.38</v>
-      </c>
-      <c r="L4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>17.37984</v>
+      </c>
+      <c r="M4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46225</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5">
+        <v>1.401</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.51</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>30.2</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>1.54</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>30.8</v>
       </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5">
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46225</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6">
+        <v>1.401</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.51</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>58.89</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>1.54</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>60.06</v>
       </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6">
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46230</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7">
+        <v>1.401</v>
+      </c>
+      <c r="I7" s="1">
         <v>1.53</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>30.6</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>1.56</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>31.2</v>
       </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7">
+      <c r="M7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46233</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8">
+        <v>1.449</v>
+      </c>
+      <c r="I8" s="1">
         <v>1.52</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>30.4</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>1.55</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>31</v>
       </c>
-      <c r="L8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8">
+      <c r="M8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46234</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>36.33</v>
+        <v>36.328</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
         <v>0.63</v>
       </c>
-      <c r="I9" s="1">
-        <v>22.89</v>
-      </c>
       <c r="J9">
+        <v>22.88664</v>
+      </c>
+      <c r="K9" s="1">
         <v>0.64</v>
       </c>
-      <c r="K9" s="1">
-        <v>23.25</v>
-      </c>
-      <c r="L9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>23.24992</v>
+      </c>
+      <c r="M9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -987,49 +1017,49 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="7">
-        <v>120.67</v>
+        <v>120.663</v>
       </c>
       <c r="C14" s="7">
         <v>4</v>
       </c>
       <c r="D14" s="8">
-        <v>0.627579</v>
+        <v>0.627557</v>
       </c>
       <c r="E14" s="7">
-        <v>75.73</v>
+        <v>75.72</v>
       </c>
       <c r="F14" s="7">
         <v>76.93000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="7">
         <v>99</v>
@@ -1047,19 +1077,19 @@
         <v>153.06</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="10">
-        <v>219.67</v>
+        <v>219.663</v>
       </c>
       <c r="C16" s="10">
         <v>8</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="10">
-        <v>225.82</v>
+        <v>225.81</v>
       </c>
       <c r="F16" s="10">
         <v>229.99</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="49">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -171,9 +168,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -267,10 +264,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -578,13 +575,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -627,389 +624,362 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>29.476</v>
       </c>
       <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>18.275</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>18.57</v>
+      </c>
+      <c r="L2" t="s">
         <v>27</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="J2">
-        <v>18.27512</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L2" s="1">
-        <v>18.56988</v>
-      </c>
-      <c r="M2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46224</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>27.703</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I3" s="1">
-        <v>0.63</v>
+        <v>17.453</v>
       </c>
       <c r="J3">
-        <v>17.45289</v>
+        <v>0.64</v>
       </c>
       <c r="K3" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L3" s="1">
-        <v>17.72992</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3">
+        <v>17.73</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46224</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>27.156</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I4" s="1">
-        <v>0.63</v>
+        <v>17.108</v>
       </c>
       <c r="J4">
-        <v>17.10828</v>
+        <v>0.64</v>
       </c>
       <c r="K4" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L4" s="1">
-        <v>17.37984</v>
-      </c>
-      <c r="M4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N4">
+        <v>17.38</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46225</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I5" s="1">
-        <v>1.51</v>
+        <v>30.2</v>
       </c>
       <c r="J5">
-        <v>30.2</v>
+        <v>1.54</v>
       </c>
       <c r="K5" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L5" s="1">
         <v>30.8</v>
       </c>
-      <c r="M5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5">
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46225</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I6" s="1">
-        <v>1.51</v>
+        <v>58.89</v>
       </c>
       <c r="J6">
-        <v>58.89</v>
+        <v>1.54</v>
       </c>
       <c r="K6" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L6" s="1">
         <v>60.06</v>
       </c>
-      <c r="M6" t="s">
-        <v>32</v>
-      </c>
-      <c r="N6">
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46230</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7">
-        <v>1.401</v>
+        <v>1.53</v>
       </c>
       <c r="I7" s="1">
-        <v>1.53</v>
+        <v>30.6</v>
       </c>
       <c r="J7">
-        <v>30.6</v>
+        <v>1.56</v>
       </c>
       <c r="K7" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L7" s="1">
         <v>31.2</v>
       </c>
-      <c r="M7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N7">
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46233</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I8" s="1">
-        <v>1.52</v>
+        <v>30.4</v>
       </c>
       <c r="J8">
-        <v>30.4</v>
+        <v>1.55</v>
       </c>
       <c r="K8" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L8" s="1">
         <v>31</v>
       </c>
-      <c r="M8" t="s">
-        <v>34</v>
-      </c>
-      <c r="N8">
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46234</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9">
         <v>36.328</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I9" s="1">
-        <v>0.63</v>
+        <v>22.887</v>
       </c>
       <c r="J9">
-        <v>22.88664</v>
+        <v>0.64</v>
       </c>
       <c r="K9" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L9" s="1">
-        <v>23.24992</v>
-      </c>
-      <c r="M9" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9">
+        <v>23.25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
+      <c r="N9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="4" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1017,69 +987,69 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="E13" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="7">
         <v>120.663</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <v>4</v>
       </c>
       <c r="D14" s="8">
-        <v>0.627557</v>
-      </c>
-      <c r="E14" s="7">
-        <v>75.72</v>
-      </c>
-      <c r="F14" s="7">
+        <v>0.628</v>
+      </c>
+      <c r="E14" s="8">
+        <v>75.723</v>
+      </c>
+      <c r="F14" s="8">
         <v>76.93000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:14">
       <c r="A15" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="7">
         <v>99</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <v>4</v>
       </c>
       <c r="D15" s="8">
-        <v>1.516061</v>
-      </c>
-      <c r="E15" s="7">
+        <v>1.516</v>
+      </c>
+      <c r="E15" s="8">
         <v>150.09</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="8">
         <v>153.06</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:14">
       <c r="A16" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="10">
         <v>219.663</v>
@@ -1089,7 +1059,7 @@
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="10">
-        <v>225.81</v>
+        <v>225.813</v>
       </c>
       <c r="F16" s="10">
         <v>229.99</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,13 +55,13 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>В7240ВР</t>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>В8992ВР</t>
@@ -76,9 +73,6 @@
     <t>В0233РС</t>
   </si>
   <si>
-    <t>78970155027720568</t>
-  </si>
-  <si>
     <t>78970155027720550</t>
   </si>
   <si>
@@ -94,55 +88,22 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:03:00</t>
-  </si>
-  <si>
-    <t>12:54:00</t>
-  </si>
-  <si>
-    <t>14:04:00</t>
-  </si>
-  <si>
-    <t>11:22:00</t>
-  </si>
-  <si>
-    <t>11:25:00</t>
-  </si>
-  <si>
-    <t>14:28:00</t>
-  </si>
-  <si>
-    <t>11:45:00</t>
-  </si>
-  <si>
-    <t>14:36:00</t>
-  </si>
-  <si>
-    <t>3234862370 3234862370</t>
-  </si>
-  <si>
-    <t>3235107979 3235107979</t>
-  </si>
-  <si>
-    <t>3235140740 3235140740</t>
-  </si>
-  <si>
-    <t>3235182898 3235182898</t>
-  </si>
-  <si>
-    <t>3235182899 3235182899</t>
-  </si>
-  <si>
-    <t>3235415080 3235415080</t>
-  </si>
-  <si>
-    <t>3235556136 3235556136</t>
-  </si>
-  <si>
-    <t>3235622040 3235622040</t>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>16:26</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>11:07</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА</t>
@@ -168,9 +129,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -264,10 +225,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -571,17 +532,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -621,453 +581,344 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46239</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>31.682</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>20.593</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>20.91</v>
+      </c>
+      <c r="K2" t="s">
         <v>24</v>
       </c>
-      <c r="F2">
-        <v>29.476</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2">
-        <v>0.62</v>
-      </c>
-      <c r="I2" s="1">
-        <v>18.275</v>
-      </c>
-      <c r="J2">
-        <v>0.63</v>
-      </c>
-      <c r="K2" s="1">
-        <v>18.57</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>230547</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46224</v>
+        <v>46239</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>27.703</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.52</v>
       </c>
       <c r="H3">
-        <v>0.63</v>
+        <v>30.4</v>
       </c>
       <c r="I3" s="1">
-        <v>17.453</v>
+        <v>1.55</v>
       </c>
       <c r="J3">
-        <v>0.64</v>
-      </c>
-      <c r="K3" s="1">
-        <v>17.73</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>289740</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
-        <v>46224</v>
+        <v>46244</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>27.156</v>
-      </c>
-      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H4">
+        <v>30.4</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J4">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
         <v>26</v>
       </c>
-      <c r="H4">
-        <v>0.63</v>
-      </c>
-      <c r="I4" s="1">
-        <v>17.108</v>
-      </c>
-      <c r="J4">
-        <v>0.64</v>
-      </c>
-      <c r="K4" s="1">
-        <v>17.38</v>
-      </c>
-      <c r="L4" t="s">
-        <v>29</v>
+      <c r="L4">
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>234419</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
-        <v>46225</v>
+        <v>46244</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
       <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>37</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H5">
+        <v>56.24</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J5">
+        <v>57.35</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>234514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5">
+      <c r="F6">
+        <v>37.015</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H6">
+        <v>24.06</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J6">
+        <v>24.43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>235279</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5">
-        <v>1.51</v>
-      </c>
-      <c r="I5" s="1">
-        <v>30.2</v>
-      </c>
-      <c r="J5">
-        <v>1.54</v>
-      </c>
-      <c r="K5" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46225</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E7" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6">
-        <v>1.51</v>
-      </c>
-      <c r="I6" s="1">
-        <v>58.89</v>
-      </c>
-      <c r="J6">
-        <v>1.54</v>
-      </c>
-      <c r="K6" s="1">
-        <v>60.06</v>
-      </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3">
-        <v>46230</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
       </c>
       <c r="F7">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
-        <v>26</v>
+      <c r="G7" s="1">
+        <v>1.52</v>
       </c>
       <c r="H7">
-        <v>1.53</v>
+        <v>30.4</v>
       </c>
       <c r="I7" s="1">
-        <v>30.6</v>
+        <v>1.55</v>
       </c>
       <c r="J7">
-        <v>1.56</v>
-      </c>
-      <c r="K7" s="1">
-        <v>31.2</v>
-      </c>
-      <c r="L7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>162866</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="3">
-        <v>46233</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="7">
+        <v>97</v>
+      </c>
+      <c r="C12" s="7">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="E12" s="7">
+        <v>147.44</v>
+      </c>
+      <c r="F12" s="7">
+        <v>150.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8">
-        <v>1.52</v>
-      </c>
-      <c r="I8" s="1">
-        <v>30.4</v>
-      </c>
-      <c r="J8">
-        <v>1.55</v>
-      </c>
-      <c r="K8" s="1">
-        <v>31</v>
-      </c>
-      <c r="L8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3">
-        <v>46234</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9">
-        <v>36.328</v>
-      </c>
-      <c r="G9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9">
-        <v>0.63</v>
-      </c>
-      <c r="I9" s="1">
-        <v>22.887</v>
-      </c>
-      <c r="J9">
-        <v>0.64</v>
-      </c>
-      <c r="K9" s="1">
-        <v>23.25</v>
-      </c>
-      <c r="L9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="7">
-        <v>120.663</v>
-      </c>
-      <c r="C14" s="8">
-        <v>4</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0.628</v>
-      </c>
-      <c r="E14" s="8">
-        <v>75.723</v>
-      </c>
-      <c r="F14" s="8">
-        <v>76.93000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="7">
-        <v>99</v>
-      </c>
-      <c r="C15" s="8">
-        <v>4</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1.516</v>
-      </c>
-      <c r="E15" s="8">
-        <v>150.09</v>
-      </c>
-      <c r="F15" s="8">
-        <v>153.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="10">
-        <v>219.663</v>
-      </c>
-      <c r="C16" s="10">
-        <v>8</v>
-      </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="10">
-        <v>225.813</v>
-      </c>
-      <c r="F16" s="10">
-        <v>229.99</v>
+      <c r="B13" s="7">
+        <v>68.697</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="E13" s="7">
+        <v>44.65</v>
+      </c>
+      <c r="F13" s="7">
+        <v>45.34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="10">
+        <v>165.697</v>
+      </c>
+      <c r="C14" s="10">
+        <v>6</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="10">
+        <v>192.09</v>
+      </c>
+      <c r="F14" s="10">
+        <v>195.69</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="55">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,55 +58,109 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Цар Освободител</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>В0235РС</t>
+  </si>
+  <si>
+    <t>В0233РС</t>
+  </si>
+  <si>
+    <t>В7240ВР</t>
   </si>
   <si>
     <t>В8992ВР</t>
   </si>
   <si>
-    <t>В0235РС</t>
-  </si>
-  <si>
-    <t>В0233РС</t>
+    <t>78970155027720543</t>
+  </si>
+  <si>
+    <t>78970155027720535</t>
+  </si>
+  <si>
+    <t>78970155027720568</t>
   </si>
   <si>
     <t>78970155027720550</t>
   </si>
   <si>
-    <t>78970155027720543</t>
-  </si>
-  <si>
-    <t>78970155027720535</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>16:26</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>11:07</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:39:00</t>
+  </si>
+  <si>
+    <t>08:26:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>14:52:00</t>
+  </si>
+  <si>
+    <t>08:34:00</t>
+  </si>
+  <si>
+    <t>10:37:00</t>
+  </si>
+  <si>
+    <t>08:33:00</t>
+  </si>
+  <si>
+    <t>08:35:00</t>
+  </si>
+  <si>
+    <t>09:04:00</t>
+  </si>
+  <si>
+    <t>17:20:00</t>
+  </si>
+  <si>
+    <t>3236525854 3236525854</t>
+  </si>
+  <si>
+    <t>3236629989 3236629989</t>
+  </si>
+  <si>
+    <t>3236657776 3236657776</t>
+  </si>
+  <si>
+    <t>3236716718 3236716718</t>
+  </si>
+  <si>
+    <t>3236848480 3236848480</t>
+  </si>
+  <si>
+    <t>3236906663 3236906663</t>
+  </si>
+  <si>
+    <t>3236943900 3236943900</t>
+  </si>
+  <si>
+    <t>3236954827 3236954827</t>
+  </si>
+  <si>
+    <t>3237126478 3237126478</t>
+  </si>
+  <si>
+    <t>3237213770 3237213770</t>
   </si>
   <si>
     <t>Общи литри по продукт / РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА</t>
@@ -128,10 +185,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -211,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -225,10 +283,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -532,16 +592,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -581,344 +642,541 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46239</v>
+        <v>46251</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.409</v>
+      </c>
+      <c r="I2" s="1">
+        <v>28.18</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="K2" s="1">
+        <v>31.2</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="F2">
-        <v>31.682</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H2">
-        <v>20.593</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J2">
-        <v>20.91</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>230547</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46239</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H3">
-        <v>30.4</v>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.429</v>
       </c>
       <c r="I3" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J3">
+        <v>28.58</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K3" s="1">
+        <v>31.4</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I4" s="1">
+        <v>48.586</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K4" s="1">
+        <v>53.72</v>
+      </c>
+      <c r="L4" t="s">
         <v>31</v>
       </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3">
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>289740</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46244</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="N4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>33.86</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I5" s="1">
+        <v>33.521</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K5" s="1">
+        <v>22.348</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H4">
-        <v>30.4</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J4">
-        <v>31</v>
-      </c>
-      <c r="K4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4">
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.439</v>
+      </c>
+      <c r="I6" s="1">
+        <v>28.78</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K6" s="1">
+        <v>31.4</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>234419</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46244</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>37</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H5">
-        <v>56.24</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J5">
-        <v>57.35</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>234514</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46245</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>37.015</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H6">
-        <v>24.06</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J6">
-        <v>24.43</v>
-      </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>235279</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
-        <v>46247</v>
+        <v>46259</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>31.33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I7" s="1">
+        <v>31.017</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K7" s="1">
+        <v>20.678</v>
+      </c>
+      <c r="L7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8">
         <v>20</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I8" s="1">
+        <v>29.18</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K8" s="1">
+        <v>31.6</v>
+      </c>
+      <c r="L8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I9" s="1">
+        <v>14.59</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="L9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>32.24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I10" s="1">
+        <v>31.918</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K10" s="1">
+        <v>21.278</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
         <v>23</v>
       </c>
-      <c r="F7">
-        <v>20</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H7">
-        <v>30.4</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J7">
-        <v>31</v>
-      </c>
-      <c r="K7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7">
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I11" s="1">
+        <v>86.081</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="K11" s="1">
+        <v>95.58</v>
+      </c>
+      <c r="L11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="M7">
-        <v>162866</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="N11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="7">
+        <v>183</v>
+      </c>
+      <c r="C16" s="8">
         <v>7</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="7">
-        <v>97</v>
-      </c>
-      <c r="C12" s="7">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E12" s="7">
-        <v>147.44</v>
-      </c>
-      <c r="F12" s="7">
-        <v>150.35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="7">
-        <v>68.697</v>
-      </c>
-      <c r="C13" s="7">
-        <v>2</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="E13" s="7">
-        <v>44.65</v>
-      </c>
-      <c r="F13" s="7">
-        <v>45.34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="10">
-        <v>165.697</v>
-      </c>
-      <c r="C14" s="10">
-        <v>6</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10">
-        <v>192.09</v>
-      </c>
-      <c r="F14" s="10">
-        <v>195.69</v>
+      <c r="D16" s="9">
+        <v>1.4425</v>
+      </c>
+      <c r="E16" s="7">
+        <v>263.98</v>
+      </c>
+      <c r="F16" s="7">
+        <v>290.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="7">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="C17" s="8">
+        <v>3</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="E17" s="7">
+        <v>96.45999999999999</v>
+      </c>
+      <c r="F17" s="7">
+        <v>64.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="11">
+        <v>280.43</v>
+      </c>
+      <c r="C18" s="12">
+        <v>10</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="11">
+        <v>360.44</v>
+      </c>
+      <c r="F18" s="11">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА/РАЙОН МЛАДОСТ - ОБЩИНА ВАРНА.xlsx
@@ -669,10 +669,10 @@
         <v>28</v>
       </c>
       <c r="H2" s="1">
-        <v>1.409</v>
+        <v>1.53</v>
       </c>
       <c r="I2" s="1">
-        <v>28.18</v>
+        <v>30.6</v>
       </c>
       <c r="J2" s="1">
         <v>1.56</v>
@@ -713,10 +713,10 @@
         <v>28</v>
       </c>
       <c r="H3" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I3" s="1">
-        <v>28.58</v>
+        <v>30.8</v>
       </c>
       <c r="J3" s="1">
         <v>1.57</v>
@@ -757,10 +757,10 @@
         <v>28</v>
       </c>
       <c r="H4" s="1">
-        <v>1.429</v>
+        <v>1.55</v>
       </c>
       <c r="I4" s="1">
-        <v>48.586</v>
+        <v>52.7</v>
       </c>
       <c r="J4" s="1">
         <v>1.58</v>
@@ -801,10 +801,10 @@
         <v>28</v>
       </c>
       <c r="H5" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I5" s="1">
-        <v>33.521</v>
+        <v>22.009</v>
       </c>
       <c r="J5" s="1">
         <v>0.66</v>
@@ -845,10 +845,10 @@
         <v>28</v>
       </c>
       <c r="H6" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I6" s="1">
-        <v>28.78</v>
+        <v>30.8</v>
       </c>
       <c r="J6" s="1">
         <v>1.57</v>
@@ -889,10 +889,10 @@
         <v>28</v>
       </c>
       <c r="H7" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I7" s="1">
-        <v>31.017</v>
+        <v>20.364</v>
       </c>
       <c r="J7" s="1">
         <v>0.66</v>
@@ -933,10 +933,10 @@
         <v>28</v>
       </c>
       <c r="H8" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I8" s="1">
-        <v>29.18</v>
+        <v>31</v>
       </c>
       <c r="J8" s="1">
         <v>1.58</v>
@@ -977,10 +977,10 @@
         <v>28</v>
       </c>
       <c r="H9" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I9" s="1">
-        <v>14.59</v>
+        <v>15.5</v>
       </c>
       <c r="J9" s="1">
         <v>1.58</v>
@@ -1021,10 +1021,10 @@
         <v>28</v>
       </c>
       <c r="H10" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I10" s="1">
-        <v>31.918</v>
+        <v>20.956</v>
       </c>
       <c r="J10" s="1">
         <v>0.66</v>
@@ -1065,10 +1065,10 @@
         <v>28</v>
       </c>
       <c r="H11" s="1">
-        <v>1.459</v>
+        <v>1.59</v>
       </c>
       <c r="I11" s="1">
-        <v>86.081</v>
+        <v>93.81</v>
       </c>
       <c r="J11" s="1">
         <v>1.62</v>
@@ -1127,10 +1127,10 @@
         <v>7</v>
       </c>
       <c r="D16" s="9">
-        <v>1.4425</v>
+        <v>1.55852</v>
       </c>
       <c r="E16" s="7">
-        <v>263.98</v>
+        <v>285.21</v>
       </c>
       <c r="F16" s="7">
         <v>290.7</v>
@@ -1147,10 +1147,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="9">
-        <v>0.99</v>
+        <v>0.64999</v>
       </c>
       <c r="E17" s="7">
-        <v>96.45999999999999</v>
+        <v>63.33</v>
       </c>
       <c r="F17" s="7">
         <v>64.3</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="11">
-        <v>360.44</v>
+        <v>348.54</v>
       </c>
       <c r="F18" s="11">
         <v>355</v>
